--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585F3F0B-A331-43E3-AC09-A4A16D940E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A463FC-6F49-451F-A230-3DD762FAA7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
+    <sheet name="斧と木のパラメータ" sheetId="7" r:id="rId2"/>
+    <sheet name="ダメージの種類" sheetId="2" r:id="rId3"/>
+    <sheet name="想定最終ビルド一覧" sheetId="3" r:id="rId4"/>
+    <sheet name="ノーマル効果一覧" sheetId="4" r:id="rId5"/>
+    <sheet name="ユニーク効果一覧" sheetId="5" r:id="rId6"/>
+    <sheet name="ガチャ確率" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="146">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -87,9 +93,6 @@
   </si>
   <si>
     <t>Luck</t>
-  </si>
-  <si>
-    <t>WoodNum</t>
   </si>
   <si>
     <t>基礎攻撃力</t>
@@ -382,52 +385,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(斧基礎速度＋加算攻撃速度)×倍率攻撃速度</t>
-    <rPh sb="1" eb="2">
-      <t>オノ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>キソソクド</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カサン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ソクド</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>バイリツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ソクド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>基礎クリティカル＋加算クリティカル
-(オーバークリティカルダメージ)
-(最終クリティカル率ー100)×0.05</t>
-    <rPh sb="0" eb="2">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カサン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>サイシュウ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クリティカル発生時の補正値。
 基礎値は50%。</t>
     <rPh sb="6" eb="8">
@@ -471,147 +428,1556 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(基礎移動速度＋加算移動速度)×倍率移動速度</t>
+    <t>基礎回収範囲＋加算回収範囲</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>カイシュウハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎幸運＋加算幸運</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウウン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウウン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在所持している木材の数。木材はガチャに使用する。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージの種類</t>
+    <rPh sb="5" eb="7">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>接触ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>セッショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非接触ダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>ヒセッショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">斧のヒットダメージを代表に、OnHitを持つダメージのこと。
+クリティカルが発生する。
+</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終攻撃力×クリティカルダメージー相手防御力</t>
+    <rPh sb="0" eb="5">
+      <t>サイシュウコウゲキリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OnHitを持たないダメージのこと。
+特殊効果でしか発生しない。（武器種が増えたらあるかも）
+クリティカルは発生せず、基礎攻撃力のみを参照する。
+相手の防御を計算しない。</t>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トクシュ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>ブキシュ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ボウギョ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技倍率×基礎攻撃力</t>
+    <rPh sb="0" eb="1">
+      <t>ワザ</t>
+    </rPh>
     <rPh sb="1" eb="3">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>キソコウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビルド名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重要ユニーク効果</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一撃ビルド</t>
+    <rPh sb="0" eb="2">
+      <t>イチゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーバー切る</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重要なパラメータ</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終攻撃力、クリティカル率、クリティカルダメージ</t>
+    <rPh sb="0" eb="5">
+      <t>サイシュウコウゲキリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>接触ダメージを高めるビルド。高いダメージを、
+オーバー切るにより伝播させることで効率的に一層できる。</t>
+    <rPh sb="0" eb="2">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>デンパ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>イッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度範囲ビルド</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃速度と範囲を高めるビルド。
+OnHitで発動する効果を大量に発生させ、手数で攻める。</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキソクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テカズ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>セ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎攻撃力、攻撃速度、攻撃範囲</t>
+    <rPh sb="0" eb="2">
       <t>キソ</t>
     </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>コウゲキソクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材の妖精</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
     <rPh sb="3" eb="5">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ソクド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カサン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ソクド</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>バイリツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ソクド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>木材を拾う範囲。
-単位はメートルと同じ。</t>
+      <t>ヨウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回収ビルド</t>
+    <rPh sb="0" eb="2">
+      <t>カイシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材を拾うことがトリガーとなるビルド。
+最終的には歩いて回収するだけで破壊し続けるようになる。</t>
     <rPh sb="0" eb="2">
       <t>モクザイ</t>
     </rPh>
     <rPh sb="3" eb="4">
       <t>ヒロ</t>
     </rPh>
+    <rPh sb="20" eb="23">
+      <t>サイシュウテキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回収範囲、基礎攻撃力、幸運</t>
+    <rPh sb="0" eb="4">
+      <t>カイシュウハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウウン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果名</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛ぶ斧</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木の体力を超えた接触ダメージが一番近い木に伝播するようになる。
+このダメージは接触ダメージになる。</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>デンパ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>セッショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲が広がって複数にヒットした場合の処理をどうするか</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>接触ダメージを与えたとき、150%の非接触ダメージを与える斧が、
+一番近い木に飛ぶ。</t>
+    <rPh sb="0" eb="2">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>イチバンチカ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材を拾った時に30％の基礎確率で一番近くの木に100%の
+非接触ダメージを与える木材が飛ぶ。
+木材が飛ぶ確率は幸運によって100%まで伸びる。</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>キソカクリツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>ヒセッショク</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>コウウン</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変動値表</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンドウチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎クリティカル＋加算クリティカル率
+(オーバークリティカルダメージ)
+(最終クリティカル率ー100)×0.05</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力＋〇</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力×〇％</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃速度×〇％</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲×〇％</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリティカル＋〇％</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリティカルダメージ＋〇％</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度×〇％</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回収範囲＋〇</t>
+    <rPh sb="0" eb="4">
+      <t>カイシュウハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期値</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斧基礎速度×倍率攻撃速度</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t>キソソクド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎移動速度×倍率移動速度</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材を拾う範囲。
+単位はcm。</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
     <rPh sb="5" eb="7">
       <t>ハンイ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>タンイ</t>
     </rPh>
-    <rPh sb="17" eb="18">
-      <t>オナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>基礎回収範囲＋加算回収範囲</t>
-    <rPh sb="0" eb="2">
-      <t>キソ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎値表</t>
+    <rPh sb="0" eb="3">
+      <t>キソチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果一覧</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>カイシュウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カサン</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>カイシュウハンイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>運。ガチャで高レアリティの装備や効果が付きやすくなるほか、
-木材のドロップ数も僅かに増加する。</t>
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コモン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マジック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レジェンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミシック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>幸運500で最大値。</t>
+    <rPh sb="0" eb="2">
+      <t>コウウン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大値</t>
+    <rPh sb="0" eb="3">
+      <t>サイダイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レアリティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倍率</t>
+    <rPh sb="0" eb="2">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果の数</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガチャコスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率合計</t>
+    <rPh sb="0" eb="2">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベル１最大値</t>
+    <rPh sb="4" eb="7">
+      <t>サイダイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運。木材のドロップ数が増加する。
+(幸運100毎に本数＋１、余りを%として計算し＋1するか処理する)</t>
     <rPh sb="0" eb="1">
       <t>ウン</t>
     </rPh>
+    <rPh sb="2" eb="4">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウウン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ホンスウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果の計算式：木こり場レベルによる基礎値＋(変動値×木こり場レベル)×レアリティ倍率</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木こり場レベル</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防御力</t>
+    <rPh sb="0" eb="3">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斧</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎値ダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>キソチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃回数</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキカイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二刀流</t>
+    <rPh sb="0" eb="3">
+      <t>ニトウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斧を二本もち交互に振ることで、斧の基礎攻撃速度が2になる。</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーションを二つの斧を振るものに変更。by海斗</t>
+    <rPh sb="8" eb="9">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇跡のクリティカル</t>
+    <rPh sb="0" eb="2">
+      <t>キセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーバークリティカルダメージの反映倍率を150%にする。</t>
+    <rPh sb="15" eb="17">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※同じユニーク効果は重複しない</t>
+    <rPh sb="1" eb="2">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジュウフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲破壊ビルド</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃範囲を軸に範囲と火力を高めるビルド。
+ユニークを3つ使うことで完成するため構築難度が高いが、
+一振りで全て破壊できるようになる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カリョク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ナンド</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ヒトフ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質より量</t>
+    <rPh sb="0" eb="1">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーズコンボ１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーズコンボ２</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃範囲の50%を基礎攻撃力に加算する。</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="9" eb="14">
+      <t>キソコウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーズコンボ３</t>
+  </si>
+  <si>
+    <t>範囲火力</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇跡のクリティカル
+質より量
+範囲火力</t>
+    <rPh sb="0" eb="2">
+      <t>キセキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ハンイカリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一度の攻撃で当たった木の数に応じてクリティカルが+50%増える。</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
     <rPh sb="6" eb="7">
-      <t>コウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ソウビ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>コウカ</t>
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材を拾った時、回収範囲内の全ての木に50％の非接触ダメージを与える。</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ヒセッショク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>波動</t>
+    <rPh sb="0" eb="2">
+      <t>ハドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木材を拾うごとに、10秒間回収範囲＋50を得る。
+効果時間は拾うたびに更新される。</t>
+    <rPh sb="0" eb="2">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>カイシュウハンイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>片付け上手</t>
+    <rPh sb="0" eb="2">
+      <t>カタヅ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妖精ビルド</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妖精ビルドと同様に木材を拾うだけになるビルド。
+回収範囲と基礎攻撃力が大事。</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モクザイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>カイシュウハンイ</t>
+    </rPh>
+    <rPh sb="29" eb="34">
+      <t>キソコウゲキリョク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ダイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>波動
+片付け上手</t>
+    <rPh sb="0" eb="2">
+      <t>ハドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カタヅ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃範囲、最終攻撃力</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキハンイ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>サイシュウコウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛ぶ斧
+二刀流</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ニトウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度15で最大。</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動中、進行方向に貫通する80%の接触ダメージを与える斬撃を飛ばす。
+発生間隔は移動速度に応じて短くなり、0.1秒間隔が最速。</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ザンゲキ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="40" eb="44">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ミジカ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>サイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剣波</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランナー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動中、毎秒基礎攻撃力が1ずつ増加する。
+攻撃を行うか0.5秒間移動しないでいるとリセットされる。</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>キソコウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>加速する腕</t>
+    <rPh sb="0" eb="2">
+      <t>カソク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウデ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二連撃</t>
+    <rPh sb="0" eb="1">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>レン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃が2回ヒットする。</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会心の一撃</t>
+    <rPh sb="0" eb="2">
+      <t>カイシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリティカル発生時、倍率100%の非接触ダメージを基礎範囲50で発生させる。
+この範囲は攻撃範囲の影響を受ける。</t>
+    <rPh sb="6" eb="8">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="44" eb="48">
+      <t>コウゲキハンイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージを与えるたび、攻撃速度が+1%増える。
+2秒間ダメージを与えなかった場合、リセットされる。</t>
+    <rPh sb="5" eb="6">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>コウゲキソクド</t>
     </rPh>
     <rPh sb="19" eb="20">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>モクザイ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ワズ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>基礎幸運＋加算幸運</t>
-    <rPh sb="0" eb="2">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウウン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カサン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウウン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現在所持している木材の数。木材はガチャに使用する。</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショジ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>モクザイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>モクザイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー</t>
+      <t>フ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃を長押しで溜めることができる。
+溜め切ると500%の接触ダメージを与える攻撃ができる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナガオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渾身</t>
+    <rPh sb="0" eb="2">
+      <t>コンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wood</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -640,7 +2006,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -653,8 +2019,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -836,13 +2232,70 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -891,6 +2344,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -906,6 +2425,1239 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>グラフ</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ガチャ確率!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>コモン</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>ガチャ確率!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>66.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-204A-49FD-8CB4-2BAE13A7C9FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ガチャ確率!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>マジック</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>ガチャ確率!$D$2:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-204A-49FD-8CB4-2BAE13A7C9FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ガチャ確率!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>レア</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>ガチャ確率!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-204A-49FD-8CB4-2BAE13A7C9FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ガチャ確率!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>レジェンド</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>ガチャ確率!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>32.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>66.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-204A-49FD-8CB4-2BAE13A7C9FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ガチャ確率!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ミシック</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>ガチャ確率!$G$2:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-204A-49FD-8CB4-2BAE13A7C9FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1418538287"/>
+        <c:axId val="1341630479"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1418538287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1341630479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1341630479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1418538287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="グラフ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98FFCD79-4022-AB2B-5488-19BAB45FA906}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1225,18 +3977,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7185871E-55CF-4276-80F8-C63379D68509}">
-  <dimension ref="A3:D14"/>
+  <dimension ref="A3:E14"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -1247,151 +3999,1718 @@
         <v>2</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="64.8" x14ac:dyDescent="0.2">
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="64.8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+      <c r="E9" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="E10" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFC34AD-8F74-4770-A4D4-748545CC6E43}">
+  <dimension ref="A3:K10"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="26">
+        <v>1</v>
+      </c>
+      <c r="C3" s="26">
+        <v>2</v>
+      </c>
+      <c r="D3" s="26">
+        <v>3</v>
+      </c>
+      <c r="E3" s="26">
+        <v>4</v>
+      </c>
+      <c r="F3" s="26">
+        <v>5</v>
+      </c>
+      <c r="G3" s="26">
+        <v>6</v>
+      </c>
+      <c r="H3" s="26">
+        <v>7</v>
+      </c>
+      <c r="I3" s="26">
+        <v>8</v>
+      </c>
+      <c r="J3" s="26">
+        <v>9</v>
+      </c>
+      <c r="K3" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="1">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1">
+        <v>200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>600</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1600</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3500</v>
+      </c>
+      <c r="G5" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44000</v>
+      </c>
+      <c r="I5" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <v>230000</v>
+      </c>
+      <c r="K5" s="1">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1">
+        <v>160</v>
+      </c>
+      <c r="E6" s="1">
+        <v>230</v>
+      </c>
+      <c r="F6" s="1">
+        <v>650</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J6" s="1">
+        <v>7000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1">
+        <v>150</v>
+      </c>
+      <c r="G8" s="1">
+        <v>210</v>
+      </c>
+      <c r="H8" s="1">
+        <v>280</v>
+      </c>
+      <c r="I8" s="1">
+        <v>360</v>
+      </c>
+      <c r="J8" s="1">
+        <v>450</v>
+      </c>
+      <c r="K8" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="1">
+        <f>B8-B6</f>
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" ref="C9:K9" si="0">C8-C6</f>
+        <v>-20</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>-130</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>-500</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>-1090</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>-2720</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>-4640</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>-6550</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>-9450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="1">
+        <f>B5/B9</f>
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" ref="C10:K10" si="1">C5/C9</f>
+        <v>-10</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="1"/>
+        <v>-6</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>-12.307692307692308</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="1"/>
+        <v>-7</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="1"/>
+        <v>-11.009174311926605</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>-16.176470588235293</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>-21.551724137931036</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+        <v>-35.114503816793892</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="1"/>
+        <v>-48.677248677248677</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179DA126-8A4C-4559-8795-96E0CA4976AF}">
+  <dimension ref="A2:C5"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6898CF-9F5C-4660-A9C0-12B8FE75CB7C}">
+  <dimension ref="A2:D8"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B792F79E-6BDB-4478-9D12-A18909A4EB37}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="21">
+        <v>1</v>
+      </c>
+      <c r="C4" s="21">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
+        <v>3</v>
+      </c>
+      <c r="E4" s="21">
+        <v>4</v>
+      </c>
+      <c r="F4" s="21">
+        <v>5</v>
+      </c>
+      <c r="G4" s="21">
+        <v>6</v>
+      </c>
+      <c r="H4" s="21">
+        <v>7</v>
+      </c>
+      <c r="I4" s="21">
+        <v>8</v>
+      </c>
+      <c r="J4" s="21">
+        <v>9</v>
+      </c>
+      <c r="K4" s="21">
+        <v>10</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1">
+        <v>60</v>
+      </c>
+      <c r="F5" s="1">
+        <v>104</v>
+      </c>
+      <c r="G5" s="1">
+        <v>167</v>
+      </c>
+      <c r="H5" s="1">
+        <v>245</v>
+      </c>
+      <c r="I5" s="1">
+        <v>404</v>
+      </c>
+      <c r="J5" s="1">
+        <v>706</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="1">
+        <f>(K5+(B16*10))*$F$20</f>
+        <v>1672</v>
+      </c>
+      <c r="M5" s="1">
+        <f>B5+(B16*1)*$F$16</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1">
+        <v>140</v>
+      </c>
+      <c r="I6" s="1">
+        <v>210</v>
+      </c>
+      <c r="J6" s="1">
+        <v>329</v>
+      </c>
+      <c r="K6" s="1">
+        <v>450</v>
+      </c>
+      <c r="L6" s="1">
+        <f>(K6+(B17*10))*$F$20</f>
+        <v>805.6</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" ref="M6:M13" si="0">B6+(B17*1)*$F$16</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="1">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1">
+        <v>57</v>
+      </c>
+      <c r="F7" s="1">
+        <v>94</v>
+      </c>
+      <c r="G7" s="1">
+        <v>165</v>
+      </c>
+      <c r="H7" s="1">
+        <v>289</v>
+      </c>
+      <c r="I7" s="1">
+        <v>420</v>
+      </c>
+      <c r="J7" s="1">
+        <v>578</v>
+      </c>
+      <c r="K7" s="1">
+        <v>700</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" ref="L7:L13" si="1">(K7+(B18*10))*$F$20</f>
+        <v>1185.5999999999999</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1">
+        <v>94</v>
+      </c>
+      <c r="G8" s="1">
+        <v>165</v>
+      </c>
+      <c r="H8" s="1">
+        <v>289</v>
+      </c>
+      <c r="I8" s="1">
+        <v>420</v>
+      </c>
+      <c r="J8" s="1">
+        <v>578</v>
+      </c>
+      <c r="K8" s="1">
+        <v>700</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="1"/>
+        <v>1185.5999999999999</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>23</v>
+      </c>
+      <c r="J9" s="1">
+        <v>28.4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>35</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="1"/>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="1">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1">
+        <v>57</v>
+      </c>
+      <c r="F10" s="1">
+        <v>94</v>
+      </c>
+      <c r="G10" s="1">
+        <v>165</v>
+      </c>
+      <c r="H10" s="1">
+        <v>289</v>
+      </c>
+      <c r="I10" s="1">
+        <v>420</v>
+      </c>
+      <c r="J10" s="1">
+        <v>578</v>
+      </c>
+      <c r="K10" s="1">
+        <v>700</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="1"/>
+        <v>1216</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1">
+        <v>80</v>
+      </c>
+      <c r="H11" s="1">
+        <v>140</v>
+      </c>
+      <c r="I11" s="1">
+        <v>210</v>
+      </c>
+      <c r="J11" s="1">
+        <v>329</v>
+      </c>
+      <c r="K11" s="1">
+        <v>450</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>760</v>
+      </c>
+      <c r="M11" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1">
+        <v>94</v>
+      </c>
+      <c r="G12" s="1">
+        <v>165</v>
+      </c>
+      <c r="H12" s="1">
+        <v>289</v>
+      </c>
+      <c r="I12" s="1">
+        <v>420</v>
+      </c>
+      <c r="J12" s="1">
+        <v>578</v>
+      </c>
+      <c r="K12" s="1">
+        <v>700</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>1109.5999999999999</v>
+      </c>
+      <c r="M12" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1">
+        <v>35</v>
+      </c>
+      <c r="E13" s="1">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1">
+        <v>94</v>
+      </c>
+      <c r="G13" s="1">
+        <v>165</v>
+      </c>
+      <c r="H13" s="1">
+        <v>289</v>
+      </c>
+      <c r="I13" s="1">
+        <v>420</v>
+      </c>
+      <c r="J13" s="1">
+        <v>578</v>
+      </c>
+      <c r="K13" s="1">
+        <v>700</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>1109.5999999999999</v>
+      </c>
+      <c r="M13" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="D15" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="G19" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5E293-C43E-4023-BF9D-9919D5512254}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.75" customWidth="1"/>
+    <col min="3" max="3" width="56.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81821629-31B0-491D-8385-FA31A2D75117}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="C2" s="23">
+        <v>66.25</v>
+      </c>
+      <c r="D2" s="1">
+        <v>26</v>
+      </c>
+      <c r="E2" s="24">
+        <v>7.5</v>
+      </c>
+      <c r="F2" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="H2" s="1">
+        <f>SUM(C2:G2)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H11" si="0">SUM(C3:G3)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1">
+        <v>37</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20</v>
+      </c>
+      <c r="D5" s="23">
+        <v>55</v>
+      </c>
+      <c r="E5" s="1">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>90</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>135</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>20</v>
+      </c>
+      <c r="E7" s="23">
+        <v>55</v>
+      </c>
+      <c r="F7" s="1">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>270</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>405</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>102.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>810</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1215</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>26</v>
+      </c>
+      <c r="F11" s="23">
+        <v>66.25</v>
+      </c>
+      <c r="G11" s="23">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>102.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A463FC-6F49-451F-A230-3DD762FAA7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7A7D15-E4B0-47BA-AEEB-D01599E0717F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="4" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="147">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -1978,6 +1978,10 @@
   </si>
   <si>
     <t>Wood</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0.5m</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4069,8 +4073,8 @@
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3">
-        <v>100</v>
+      <c r="E8" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="64.8" x14ac:dyDescent="0.2">
@@ -4802,42 +4806,42 @@
         <v>72</v>
       </c>
       <c r="B8" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="H8" s="1">
-        <v>289</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1">
-        <v>420</v>
+        <v>22</v>
       </c>
       <c r="J8" s="1">
-        <v>578</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
-        <v>700</v>
+        <v>40</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="1"/>
-        <v>1185.5999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -5130,7 +5134,7 @@
         <v>72</v>
       </c>
       <c r="B19" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>86</v>

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7A7D15-E4B0-47BA-AEEB-D01599E0717F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3BFADB-15A5-4522-A96E-B508122D49C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="4" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="146">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -524,19 +524,6 @@
     </rPh>
     <rPh sb="38" eb="40">
       <t>ハッセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最終攻撃力×クリティカルダメージー相手防御力</t>
-    <rPh sb="0" eb="5">
-      <t>サイシュウコウゲキリョク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>ボウギョリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1981,7 +1968,16 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0.5m</t>
+    <t>最終攻撃力ー相手防御力×クリティカルダメージ</t>
+    <rPh sb="0" eb="5">
+      <t>サイシュウコウゲキリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ボウギョリョク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4006,7 +4002,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
@@ -4054,7 +4050,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3">
         <v>1</v>
@@ -4073,8 +4069,8 @@
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>146</v>
+      <c r="E8" s="3">
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="64.8" x14ac:dyDescent="0.2">
@@ -4088,7 +4084,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="15">
         <v>5</v>
@@ -4122,7 +4118,7 @@
         <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -4136,7 +4132,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>34</v>
@@ -4153,7 +4149,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>35</v>
@@ -4167,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
@@ -4195,7 +4191,7 @@
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="26">
         <v>1</v>
@@ -4230,12 +4226,12 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" s="1">
         <v>40</v>
@@ -4270,7 +4266,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -4305,12 +4301,12 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="1">
         <v>10</v>
@@ -4345,7 +4341,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1">
         <f>B8-B6</f>
@@ -4390,7 +4386,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1">
         <f>B5/B9</f>
@@ -4469,7 +4465,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.25">
@@ -4477,10 +4473,10 @@
         <v>40</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4503,86 +4499,86 @@
     <row r="2" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="D4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="48.6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>129</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4603,7 +4599,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -4616,7 +4612,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
@@ -4633,7 +4629,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="21">
         <v>1</v>
@@ -4666,15 +4662,15 @@
         <v>10</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -4717,7 +4713,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -4760,7 +4756,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -4803,7 +4799,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -4846,7 +4842,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -4889,7 +4885,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
@@ -4932,7 +4928,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -4975,7 +4971,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
@@ -5061,29 +5057,29 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="32"/>
       <c r="D15" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="36"/>
       <c r="F15" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>92</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="1">
@@ -5095,13 +5091,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1">
         <v>8</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="1">
@@ -5113,13 +5109,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1">
         <v>8</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="1">
@@ -5131,13 +5127,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="1">
@@ -5149,25 +5145,25 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="1">
         <v>1.52</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
@@ -5175,7 +5171,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1">
         <v>5</v>
@@ -5183,7 +5179,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
@@ -5226,39 +5222,39 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>37</v>
@@ -5266,130 +5262,130 @@
     </row>
     <row r="6" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>111</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>136</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>139</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>141</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="1"/>
     </row>
@@ -5418,28 +5414,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3BFADB-15A5-4522-A96E-B508122D49C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA3308C-BD6E-4923-8A95-C7371A5D3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA3308C-BD6E-4923-8A95-C7371A5D3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6175288-6C83-45EB-AF72-8581717D8748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="149">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -1977,6 +1977,95 @@
     </rPh>
     <rPh sb="8" eb="11">
       <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドロップキック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身の移動速度以下の木を即座に倒し、吹っ飛ばす。
+吹っ飛ばした木に当たった他の木には移動速度150%のダメージを与え、
+これで倒した木もまた吹っ飛ばす。</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃範囲をサイズに変更し、ノーマル効果ではあまり変わらないようにする？</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキハンイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2050,7 +2139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2289,13 +2378,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2389,6 +2489,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2407,8 +2510,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3977,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7185871E-55CF-4276-80F8-C63379D68509}">
-  <dimension ref="A3:E14"/>
+  <dimension ref="A3:E15"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -4173,6 +4276,11 @@
       </c>
       <c r="E14" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="38" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4598,32 +4706,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="32"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="33"/>
       <c r="L3" s="21"/>
       <c r="M3" s="1"/>
     </row>
@@ -5056,14 +5164,14 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="D15" s="36" t="s">
+      <c r="B15" s="33"/>
+      <c r="D15" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="21" t="s">
         <v>91</v>
       </c>
@@ -5078,10 +5186,10 @@
       <c r="B16" s="1">
         <v>10</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="32"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="1">
         <v>1</v>
       </c>
@@ -5096,10 +5204,10 @@
       <c r="B17" s="1">
         <v>8</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="32"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -5114,10 +5222,10 @@
       <c r="B18" s="1">
         <v>8</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="1">
         <v>1.2</v>
       </c>
@@ -5132,10 +5240,10 @@
       <c r="B19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="1">
         <v>1.34</v>
       </c>
@@ -5150,10 +5258,10 @@
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="1">
         <v>1.52</v>
       </c>
@@ -5212,7 +5320,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5E293-C43E-4023-BF9D-9919D5512254}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
@@ -5221,11 +5329,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
@@ -5388,6 +5496,14 @@
         <v>142</v>
       </c>
       <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A19" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6175288-6C83-45EB-AF72-8581717D8748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1E6486-195F-4EBC-B5A3-6CD1F401E0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="5" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="151">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -2069,12 +2069,38 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>コピー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスポーンする木が増えるorドロップする木が二倍になる（確率でもあり）</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -2489,6 +2515,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2509,9 +2538,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4081,7 +4107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7185871E-55CF-4276-80F8-C63379D68509}">
   <dimension ref="A3:E15"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
@@ -4090,8 +4116,8 @@
     <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="16.8" thickBot="1"/>
+    <row r="4" spans="1:5" ht="16.8" thickBot="1">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -4108,7 +4134,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="32.4">
       <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
@@ -4125,7 +4151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="32.4">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -4142,7 +4168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="32.4">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -4159,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="32.4">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -4176,7 +4202,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="64.8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="64.8">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -4193,7 +4219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="32.4">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -4210,7 +4236,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -4227,7 +4253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="32.4">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -4244,7 +4270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="32.4">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -4261,7 +4287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="16.8" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -4278,8 +4304,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="31" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4292,12 +4318,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFC34AD-8F74-4770-A4D4-748545CC6E43}">
   <dimension ref="A3:K10"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="25" t="s">
         <v>98</v>
       </c>
@@ -4332,12 +4358,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="25" t="s">
         <v>99</v>
       </c>
@@ -4372,7 +4398,7 @@
         <v>460000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="25" t="s">
         <v>100</v>
       </c>
@@ -4407,12 +4433,12 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="25" t="s">
         <v>103</v>
       </c>
@@ -4447,7 +4473,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="25" t="s">
         <v>104</v>
       </c>
@@ -4492,7 +4518,7 @@
         <v>-9450</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="25" t="s">
         <v>105</v>
       </c>
@@ -4546,15 +4572,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179DA126-8A4C-4559-8795-96E0CA4976AF}">
   <dimension ref="A2:C5"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="57.4140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16.8" thickBot="1"/>
+    <row r="3" spans="1:3" ht="16.8" thickBot="1">
       <c r="A3" s="18" t="s">
         <v>38</v>
       </c>
@@ -4565,7 +4591,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="48.6">
       <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
@@ -4576,7 +4602,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
@@ -4596,7 +4622,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6898CF-9F5C-4660-A9C0-12B8FE75CB7C}">
   <dimension ref="A2:D8"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.9140625" bestFit="1" customWidth="1"/>
@@ -4604,8 +4630,8 @@
     <col min="4" max="4" width="52.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16.8" thickBot="1"/>
+    <row r="3" spans="1:4" ht="16.8" thickBot="1">
       <c r="A3" s="18" t="s">
         <v>44</v>
       </c>
@@ -4619,7 +4645,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="32.4">
       <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
@@ -4633,7 +4659,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="32.4">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -4647,7 +4673,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="32.4">
       <c r="A6" s="1" t="s">
         <v>126</v>
       </c>
@@ -4661,7 +4687,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="48.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="48.6">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -4675,7 +4701,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="32.4">
       <c r="A8" s="1" t="s">
         <v>55</v>
       </c>
@@ -4698,44 +4724,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B792F79E-6BDB-4478-9D12-A18909A4EB37}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="28.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="34"/>
       <c r="L3" s="21"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13">
       <c r="A4" s="21" t="s">
         <v>81</v>
       </c>
@@ -4776,7 +4802,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>68</v>
       </c>
@@ -4819,7 +4845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
@@ -4862,7 +4888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>70</v>
       </c>
@@ -4905,7 +4931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
         <v>71</v>
       </c>
@@ -4948,7 +4974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
         <v>72</v>
       </c>
@@ -4991,7 +5017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
@@ -5034,7 +5060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
         <v>74</v>
       </c>
@@ -5077,7 +5103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -5120,7 +5146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5163,15 +5189,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+    <row r="15" spans="1:13">
+      <c r="A15" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="D15" s="37" t="s">
+      <c r="B15" s="34"/>
+      <c r="D15" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="38"/>
       <c r="F15" s="21" t="s">
         <v>91</v>
       </c>
@@ -5179,17 +5205,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="33"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="1">
         <v>1</v>
       </c>
@@ -5197,17 +5223,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B17" s="1">
         <v>8</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="33"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -5215,17 +5241,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="1">
         <v>8</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="33"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="1">
         <v>1.2</v>
       </c>
@@ -5233,17 +5259,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="33"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="1">
         <v>1.34</v>
       </c>
@@ -5251,17 +5277,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="33"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="1">
         <v>1.52</v>
       </c>
@@ -5269,7 +5295,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -5277,7 +5303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -5285,7 +5311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>75</v>
       </c>
@@ -5293,7 +5319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -5320,22 +5346,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5E293-C43E-4023-BF9D-9919D5512254}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="70.75" customWidth="1"/>
     <col min="3" max="3" width="56.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="16" t="s">
         <v>58</v>
       </c>
@@ -5346,7 +5372,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="32.4">
       <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
@@ -5357,7 +5383,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="32.4">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -5368,7 +5394,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="48.6">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -5379,7 +5405,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>106</v>
       </c>
@@ -5390,7 +5416,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>109</v>
       </c>
@@ -5401,7 +5427,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
@@ -5412,7 +5438,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>119</v>
       </c>
@@ -5423,7 +5449,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>123</v>
       </c>
@@ -5432,7 +5458,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="32.4">
       <c r="A12" s="1" t="s">
         <v>125</v>
       </c>
@@ -5441,7 +5467,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="32.4">
       <c r="A13" s="29" t="s">
         <v>133</v>
       </c>
@@ -5452,7 +5478,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="32.4">
       <c r="A14" s="1" t="s">
         <v>134</v>
       </c>
@@ -5461,7 +5487,7 @@
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="32.4">
       <c r="A15" s="1" t="s">
         <v>136</v>
       </c>
@@ -5470,7 +5496,7 @@
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>137</v>
       </c>
@@ -5479,7 +5505,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="32.4">
       <c r="A17" s="1" t="s">
         <v>139</v>
       </c>
@@ -5488,7 +5514,7 @@
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="32.4">
       <c r="A18" s="1" t="s">
         <v>143</v>
       </c>
@@ -5497,12 +5523,20 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="48.6">
       <c r="A19" s="29" t="s">
         <v>146</v>
       </c>
       <c r="B19" s="30" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5517,7 +5551,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81821629-31B0-491D-8385-FA31A2D75117}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.4140625" bestFit="1" customWidth="1"/>
@@ -5528,7 +5562,7 @@
     <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="16" t="s">
         <v>98</v>
       </c>
@@ -5554,7 +5588,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5581,7 +5615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5608,7 +5642,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5635,7 +5669,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5662,7 +5696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5689,7 +5723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -5716,7 +5750,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -5743,7 +5777,7 @@
         <v>103.2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -5770,7 +5804,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -5797,7 +5831,7 @@
         <v>103.2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1E6486-195F-4EBC-B5A3-6CD1F401E0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1E437E-0CEE-45BD-A2F8-BADAB9A74B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="5" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="152">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -280,51 +280,6 @@
     </rPh>
     <rPh sb="24" eb="25">
       <t>アタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>斧の攻撃範囲。
-この値に応じて接触判定が広がる。</t>
-    <rPh sb="0" eb="1">
-      <t>オノ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>コウゲキハンイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セッショク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ヒロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>斧基礎範囲×倍率範囲</t>
-    <rPh sb="0" eb="1">
-      <t>オノ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>バイリツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1493,9 +1448,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>デザイナーズコンボ３</t>
-  </si>
-  <si>
     <t>範囲火力</t>
     <rPh sb="0" eb="2">
       <t>ハンイ</t>
@@ -2092,6 +2044,65 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>カクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斧基礎範囲</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斧の攻撃範囲。
+基本的に範囲は斧に依存し変化しない。</t>
+    <rPh sb="0" eb="1">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>コウゲキハンイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オノ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イゾン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除予定</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーズコンボ３ ※削除もしくはリメイク予定</t>
+    <rPh sb="12" eb="14">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2100,7 +2111,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -4107,7 +4118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7185871E-55CF-4276-80F8-C63379D68509}">
   <dimension ref="A3:E15"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
@@ -4116,8 +4127,8 @@
     <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="16.8" thickBot="1"/>
-    <row r="4" spans="1:5" ht="16.8" thickBot="1">
+    <row r="3" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
@@ -4131,10 +4142,10 @@
         <v>22</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="32.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
@@ -4145,13 +4156,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="32.4">
+    <row r="6" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -4168,7 +4179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="32.4">
+    <row r="7" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -4179,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="32.4">
+    <row r="8" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -4193,16 +4204,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="E8" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="64.8">
+    <row r="9" spans="1:5" ht="64.8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -4210,16 +4221,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32.4">
+    <row r="10" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -4227,16 +4238,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -4244,16 +4255,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="32.4">
+    <row r="12" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -4261,16 +4272,16 @@
         <v>10</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="32.4">
+    <row r="13" spans="1:5" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -4278,35 +4289,35 @@
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.8" thickBot="1">
+    <row r="14" spans="1:5" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4318,14 +4329,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFC34AD-8F74-4770-A4D4-748545CC6E43}">
   <dimension ref="A3:K10"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="26">
         <v>1</v>
@@ -4358,14 +4369,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1">
         <v>40</v>
@@ -4398,9 +4409,9 @@
         <v>460000</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -4433,14 +4444,14 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" s="1">
         <v>10</v>
@@ -4473,9 +4484,9 @@
         <v>550</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1">
         <f>B8-B6</f>
@@ -4518,9 +4529,9 @@
         <v>-9450</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B10" s="1">
         <f>B5/B9</f>
@@ -4572,17 +4583,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179DA126-8A4C-4559-8795-96E0CA4976AF}">
   <dimension ref="A2:C5"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="57.4140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="16.8" thickBot="1"/>
-    <row r="3" spans="1:3" ht="16.8" thickBot="1">
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>2</v>
@@ -4591,26 +4602,26 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="48.6">
+    <row r="4" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="65.400000000000006" thickBot="1">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4622,7 +4633,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6898CF-9F5C-4660-A9C0-12B8FE75CB7C}">
   <dimension ref="A2:D8"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.9140625" bestFit="1" customWidth="1"/>
@@ -4630,89 +4641,89 @@
     <col min="4" max="4" width="52.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="16.8" thickBot="1"/>
-    <row r="3" spans="1:4" ht="16.8" thickBot="1">
+    <row r="2" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="32.4">
-      <c r="A4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="32.4">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="32.4">
-      <c r="A6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="48.6">
-      <c r="A7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="32.4">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4723,17 +4734,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B792F79E-6BDB-4478-9D12-A18909A4EB37}">
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -4744,9 +4755,9 @@
       <c r="H1" s="36"/>
       <c r="I1" s="36"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" s="37"/>
       <c r="C3" s="37"/>
@@ -4761,9 +4772,9 @@
       <c r="L3" s="21"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" s="21">
         <v>1</v>
@@ -4796,15 +4807,15 @@
         <v>10</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -4845,9 +4856,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -4888,9 +4899,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -4931,9 +4942,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -4973,10 +4984,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -5017,9 +5031,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
@@ -5060,9 +5074,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -5103,9 +5117,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
@@ -5146,7 +5160,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5189,31 +5203,31 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B15" s="34"/>
       <c r="D15" s="38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="1">
@@ -5223,15 +5237,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" s="1">
         <v>8</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="1">
@@ -5241,15 +5255,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1">
         <v>8</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="1">
@@ -5259,15 +5273,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="1">
@@ -5277,49 +5291,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="1">
         <v>1.52</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -5347,196 +5361,196 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5E293-C43E-4023-BF9D-9919D5512254}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="70.75" customWidth="1"/>
     <col min="3" max="3" width="56.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="16" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="32.4">
-      <c r="A4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="B5" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="32.4">
-      <c r="A5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="48.6">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>65</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B8" s="14" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>110</v>
-      </c>
       <c r="C8" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="C10" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" ht="32.4">
-      <c r="A12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="32.4">
+    <row r="13" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="32.4">
-      <c r="A14" s="1" t="s">
+      <c r="B15" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B16" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" ht="32.4">
-      <c r="A15" s="1" t="s">
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
+      <c r="B17" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" ht="32.4">
-      <c r="A17" s="1" t="s">
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" ht="32.4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3" ht="32.4">
-      <c r="A18" s="1" t="s">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" ht="48.6" x14ac:dyDescent="0.2">
+      <c r="A19" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3" ht="48.6">
-      <c r="A19" s="29" t="s">
+      <c r="B19" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B20" s="30" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5551,7 +5565,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81821629-31B0-491D-8385-FA31A2D75117}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.4140625" bestFit="1" customWidth="1"/>
@@ -5562,33 +5576,33 @@
     <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>86</v>
-      </c>
       <c r="H1" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5615,7 +5629,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5642,7 +5656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5669,7 +5683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5696,7 +5710,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5723,7 +5737,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -5750,7 +5764,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -5777,7 +5791,7 @@
         <v>103.2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -5804,7 +5818,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -5831,7 +5845,7 @@
         <v>103.2</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>

--- a/設定資料xlsx.xlsx
+++ b/設定資料xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zeida\ドキュメント\卒研\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1E437E-0CEE-45BD-A2F8-BADAB9A74B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EC85B1-ECF9-4378-84F8-D5ED9FC6B9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="5" xr2:uid="{C7D81F84-D63D-4AD2-A31B-55004214F904}"/>
   </bookViews>
   <sheets>
     <sheet name="パラメータ" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="156">
   <si>
     <t>パラメータ</t>
     <phoneticPr fontId="1"/>
@@ -2103,6 +2103,55 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くるくる～</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃が長押しするほど速くなる回転攻撃に変化する。</t>
+    <rPh sb="0" eb="4">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナガオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体当たり</t>
+    <rPh sb="0" eb="2">
+      <t>タイア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木にぶつかると何か依存でダメージを与える</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イゾン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2432,7 +2481,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2529,9 +2578,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2549,6 +2595,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4743,32 +4798,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="33"/>
       <c r="L3" s="21"/>
       <c r="M3" s="1"/>
     </row>
@@ -5204,14 +5259,14 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="D15" s="38" t="s">
+      <c r="B15" s="33"/>
+      <c r="D15" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="38"/>
+      <c r="E15" s="37"/>
       <c r="F15" s="21" t="s">
         <v>89</v>
       </c>
@@ -5226,10 +5281,10 @@
       <c r="B16" s="1">
         <v>10</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="1">
         <v>1</v>
       </c>
@@ -5244,10 +5299,10 @@
       <c r="B17" s="1">
         <v>8</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="34"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -5262,10 +5317,10 @@
       <c r="B18" s="1">
         <v>8</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="34"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="1">
         <v>1.2</v>
       </c>
@@ -5280,10 +5335,10 @@
       <c r="B19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="34"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="1">
         <v>1.34</v>
       </c>
@@ -5298,10 +5353,10 @@
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="34"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="1">
         <v>1.52</v>
       </c>
@@ -5360,7 +5415,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C5E293-C43E-4023-BF9D-9919D5512254}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
@@ -5369,11 +5424,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
@@ -5551,6 +5606,22 @@
       </c>
       <c r="B20" s="30" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
